--- a/assets/通报模板.xlsx
+++ b/assets/通报模板.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenzhida/Desktop/双畅享首销通报工具/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenzhida/Desktop/sales_tool/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6606E717-620A-964B-ABEA-6B9847AB045B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58B000B-FA6A-8746-9361-7FD536FA3704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="112">
   <si>
     <t>华为畅享 90 Plus 8GB+256GB 星空黑 双卡 全网通版</t>
   </si>
@@ -423,6 +423,10 @@
   </si>
   <si>
     <t>云南九机电子产品有限公司</t>
+  </si>
+  <si>
+    <t>曲靖沾益联鸿通讯有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1194,7 +1198,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E010BAD6-630B-3E4A-AB71-C40B8BCE4601}">
-  <dimension ref="A1:AJ34"/>
+  <dimension ref="A1:AJ35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="37.6640625" bestFit="1" customWidth="1"/>
@@ -1433,7 +1437,7 @@
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="18">
-        <f t="shared" ref="G3:G34" si="0">F3/E3</f>
+        <f t="shared" ref="G3:G35" si="0">F3/E3</f>
         <v>0</v>
       </c>
       <c r="H3" s="1">
@@ -1441,7 +1445,7 @@
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="18">
-        <f t="shared" ref="J3:J34" si="1">I3/H3</f>
+        <f t="shared" ref="J3:J35" si="1">I3/H3</f>
         <v>0</v>
       </c>
       <c r="K3" s="1">
@@ -1449,7 +1453,7 @@
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="18">
-        <f t="shared" ref="M3:M34" si="2">L3/K3</f>
+        <f t="shared" ref="M3:M35" si="2">L3/K3</f>
         <v>0</v>
       </c>
       <c r="N3" s="1">
@@ -1457,7 +1461,7 @@
       </c>
       <c r="O3" s="1"/>
       <c r="P3" s="18">
-        <f t="shared" ref="P3:P34" si="3">O3/N3</f>
+        <f t="shared" ref="P3:P35" si="3">O3/N3</f>
         <v>0</v>
       </c>
       <c r="Q3" s="1">
@@ -1465,7 +1469,7 @@
       </c>
       <c r="R3" s="1"/>
       <c r="S3" s="18">
-        <f t="shared" ref="S3:S34" si="4">R3/Q3</f>
+        <f t="shared" ref="S3:S35" si="4">R3/Q3</f>
         <v>0</v>
       </c>
       <c r="T3" s="1">
@@ -1473,7 +1477,7 @@
       </c>
       <c r="U3" s="1"/>
       <c r="V3" s="18">
-        <f t="shared" ref="V3:V34" si="5">U3/T3</f>
+        <f t="shared" ref="V3:V35" si="5">U3/T3</f>
         <v>0</v>
       </c>
       <c r="W3" s="1">
@@ -4024,153 +4028,233 @@
       <c r="AJ33" s="1"/>
     </row>
     <row r="34" spans="1:36" ht="18">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" s="3">
+        <v>1</v>
+      </c>
+      <c r="C34" s="3">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3">
+        <v>1</v>
+      </c>
+      <c r="E34" s="1">
+        <v>0</v>
+      </c>
+      <c r="F34" s="1"/>
+      <c r="G34" s="18" t="e">
+        <f t="shared" ref="G34" si="12">F34/E34</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H34" s="1">
+        <v>1</v>
+      </c>
+      <c r="I34" s="1"/>
+      <c r="J34" s="18">
+        <f t="shared" ref="J34" si="13">I34/H34</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="1">
+        <v>1</v>
+      </c>
+      <c r="L34" s="1"/>
+      <c r="M34" s="18">
+        <f t="shared" ref="M34" si="14">L34/K34</f>
+        <v>0</v>
+      </c>
+      <c r="N34" s="1">
+        <v>0</v>
+      </c>
+      <c r="O34" s="1"/>
+      <c r="P34" s="18" t="e">
+        <f t="shared" ref="P34" si="15">O34/N34</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q34" s="1">
+        <v>1</v>
+      </c>
+      <c r="R34" s="1"/>
+      <c r="S34" s="18">
+        <f t="shared" ref="S34" si="16">R34/Q34</f>
+        <v>0</v>
+      </c>
+      <c r="T34" s="1">
+        <v>1</v>
+      </c>
+      <c r="U34" s="1"/>
+      <c r="V34" s="18">
+        <f t="shared" ref="V34" si="17">U34/T34</f>
+        <v>0</v>
+      </c>
+      <c r="W34" s="1"/>
+      <c r="X34" s="1"/>
+      <c r="Y34" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="1"/>
+      <c r="AA34" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB34" s="1"/>
+      <c r="AC34" s="1"/>
+      <c r="AD34" s="1"/>
+      <c r="AE34" s="1"/>
+      <c r="AF34" s="1"/>
+      <c r="AG34" s="1"/>
+      <c r="AH34" s="1"/>
+      <c r="AI34" s="1"/>
+      <c r="AJ34" s="1"/>
+    </row>
+    <row r="35" spans="1:36" ht="18">
+      <c r="A35" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="2">
-        <f t="shared" ref="B34:AJ34" si="12">SUM(B2:B32)</f>
+      <c r="B35" s="2">
+        <f t="shared" ref="B35:AJ35" si="18">SUM(B2:B32)</f>
         <v>176</v>
       </c>
-      <c r="C34" s="2">
-        <f t="shared" si="12"/>
+      <c r="C35" s="2">
+        <f t="shared" si="18"/>
         <v>181</v>
       </c>
-      <c r="D34" s="2">
-        <f t="shared" si="12"/>
+      <c r="D35" s="2">
+        <f t="shared" si="18"/>
         <v>357</v>
       </c>
-      <c r="E34" s="2">
-        <f t="shared" si="12"/>
+      <c r="E35" s="2">
+        <f t="shared" si="18"/>
         <v>25</v>
       </c>
-      <c r="F34" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="G34" s="19">
+      <c r="F35" s="2">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H34" s="2">
-        <f t="shared" si="12"/>
+      <c r="H35" s="2">
+        <f t="shared" si="18"/>
         <v>52</v>
       </c>
-      <c r="I34" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="J34" s="19">
+      <c r="I35" s="2">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K34" s="2">
-        <f t="shared" si="12"/>
+      <c r="K35" s="2">
+        <f t="shared" si="18"/>
         <v>83</v>
       </c>
-      <c r="L34" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M34" s="19">
+      <c r="L35" s="2">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="M35" s="19">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N34" s="2">
-        <f t="shared" si="12"/>
+      <c r="N35" s="2">
+        <f t="shared" si="18"/>
         <v>25</v>
       </c>
-      <c r="O34" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="P34" s="19">
+      <c r="O35" s="2">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P35" s="19">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q34" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q35" s="2">
+        <f t="shared" si="18"/>
         <v>52</v>
       </c>
-      <c r="R34" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S34" s="19">
+      <c r="R35" s="2">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="19">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="T34" s="2">
-        <f t="shared" si="12"/>
+      <c r="T35" s="2">
+        <f t="shared" si="18"/>
         <v>83</v>
       </c>
-      <c r="U34" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="V34" s="19">
+      <c r="U35" s="2">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="19">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="W34" s="2">
-        <f t="shared" si="12"/>
+      <c r="W35" s="2">
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
-      <c r="X34" s="2">
-        <f t="shared" si="12"/>
+      <c r="X35" s="2">
+        <f t="shared" si="18"/>
         <v>29</v>
       </c>
-      <c r="Y34" s="2">
-        <f t="shared" si="12"/>
+      <c r="Y35" s="2">
+        <f t="shared" si="18"/>
         <v>5</v>
       </c>
-      <c r="Z34" s="2">
-        <f t="shared" si="12"/>
+      <c r="Z35" s="2">
+        <f t="shared" si="18"/>
         <v>33</v>
       </c>
-      <c r="AA34" s="2">
-        <f t="shared" si="12"/>
+      <c r="AA35" s="2">
+        <f t="shared" si="18"/>
         <v>80</v>
       </c>
-      <c r="AB34" s="2">
-        <f t="shared" si="12"/>
+      <c r="AB35" s="2">
+        <f t="shared" si="18"/>
         <v>20</v>
       </c>
-      <c r="AC34" s="2">
-        <f t="shared" si="12"/>
+      <c r="AC35" s="2">
+        <f t="shared" si="18"/>
         <v>14</v>
       </c>
-      <c r="AD34" s="2">
-        <f t="shared" si="12"/>
+      <c r="AD35" s="2">
+        <f t="shared" si="18"/>
         <v>41</v>
       </c>
-      <c r="AE34" s="2">
-        <f t="shared" si="12"/>
+      <c r="AE35" s="2">
+        <f t="shared" si="18"/>
         <v>23</v>
       </c>
-      <c r="AF34" s="2">
-        <f t="shared" si="12"/>
+      <c r="AF35" s="2">
+        <f t="shared" si="18"/>
         <v>47</v>
       </c>
-      <c r="AG34" s="2">
-        <f t="shared" si="12"/>
+      <c r="AG35" s="2">
+        <f t="shared" si="18"/>
         <v>10</v>
       </c>
-      <c r="AH34" s="2">
-        <f t="shared" si="12"/>
+      <c r="AH35" s="2">
+        <f t="shared" si="18"/>
         <v>10</v>
       </c>
-      <c r="AI34" s="2">
-        <f t="shared" si="12"/>
+      <c r="AI35" s="2">
+        <f t="shared" si="18"/>
         <v>12</v>
       </c>
-      <c r="AJ34" s="2">
-        <f t="shared" si="12"/>
+      <c r="AJ35" s="2">
+        <f t="shared" si="18"/>
         <v>24</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G33">
+  <conditionalFormatting sqref="G2:G34">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -4182,7 +4266,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J33">
+  <conditionalFormatting sqref="J2:J34">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -4194,7 +4278,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M33">
+  <conditionalFormatting sqref="M2:M34">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -4206,7 +4290,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P33">
+  <conditionalFormatting sqref="P2:P34">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -4218,7 +4302,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S33">
+  <conditionalFormatting sqref="S2:S34">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -4230,7 +4314,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V33">
+  <conditionalFormatting sqref="V2:V34">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
